--- a/results/extensibility/run/results.xlsx
+++ b/results/extensibility/run/results.xlsx
@@ -1559,19 +1559,19 @@
         <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>99.99999999999999</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
         <v>80</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>4.944420000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.045</v>
+        <v>0.04500000000000001</v>
       </c>
       <c r="R2" t="n">
         <v>12.32876712328767</v>
@@ -1615,7 +1615,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-3.552713678800501e-14</v>
       </c>
     </row>
     <row r="3">
@@ -1669,7 +1669,7 @@
         <v>153.0518</v>
       </c>
       <c r="P3" t="n">
-        <v>6.887331000000001</v>
+        <v>6.887331</v>
       </c>
       <c r="Q3" t="n">
         <v>0.04500000000000001</v>
@@ -1743,13 +1743,13 @@
         <v>30.82224430000005</v>
       </c>
       <c r="N4" t="n">
-        <v>203.1881999999999</v>
+        <v>203.1882</v>
       </c>
       <c r="O4" t="n">
-        <v>203.1881999999999</v>
+        <v>203.1882</v>
       </c>
       <c r="P4" t="n">
-        <v>5.790863699999997</v>
+        <v>5.790863699999999</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0285</v>
@@ -1761,7 +1761,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>26.28542482500007</v>
+        <v>26.28542482500006</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>2.842170943040401e-14</v>
       </c>
     </row>
     <row r="5">
@@ -1829,7 +1829,7 @@
         <v>261.7714</v>
       </c>
       <c r="P5" t="n">
-        <v>3.141256800000001</v>
+        <v>3.1412568</v>
       </c>
       <c r="Q5" t="n">
         <v>0.012</v>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>-2.842170943040401e-14</v>
       </c>
     </row>
     <row r="6">
@@ -1962,7 +1962,7 @@
         <v>390</v>
       </c>
       <c r="G7" t="n">
-        <v>250.0000000000001</v>
+        <v>250</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -2001,7 +2001,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>51.78118430000013</v>
+        <v>51.78118430000014</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-7.105427357601002e-14</v>
+        <v>4.263256414560601e-14</v>
       </c>
     </row>
     <row r="8">
@@ -2069,7 +2069,7 @@
         <v>455.4656</v>
       </c>
       <c r="P8" t="n">
-        <v>5.465587200000001</v>
+        <v>5.4655872</v>
       </c>
       <c r="Q8" t="n">
         <v>0.012</v>
@@ -2081,7 +2081,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>55.47984670000017</v>
+        <v>55.47984670000019</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -9777,10 +9777,10 @@
         <v>161.7714</v>
       </c>
       <c r="M21" t="n">
-        <v>161.7714000000001</v>
+        <v>161.7714</v>
       </c>
       <c r="N21" t="n">
-        <v>161.7714000000001</v>
+        <v>161.7714</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
@@ -11202,10 +11202,10 @@
         <v>85.46559999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>85.46560000000001</v>
+        <v>85.46559999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>85.46560000000001</v>
+        <v>85.46559999999999</v>
       </c>
       <c r="O40" t="n">
         <v>1</v>
@@ -11836,7 +11836,7 @@
         <v>102.3336</v>
       </c>
       <c r="F7" t="n">
-        <v>37.2824526960001</v>
+        <v>37.28245269600009</v>
       </c>
       <c r="G7" t="n">
         <v>82</v>
@@ -12331,7 +12331,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>0.97</v>
@@ -27737,7 +27737,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -27817,7 +27817,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">

--- a/results/extensibility/run/results.xlsx
+++ b/results/extensibility/run/results.xlsx
@@ -423,13 +423,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>TerraPlan export</t>
+          <t>Выгрузка TerraPlan, версия</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>plan_id</t>
+          <t>план (plan_id)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>scenario_id</t>
+          <t>сценарий (scenario_id)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -465,96 +465,240 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>feasible</t>
+          <t>план исполним</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>unit:fuel</t>
+          <t>жёстких нарушений / отклонений от ориентиров / предупреждений</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>0 / 0 / 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>unit:money</t>
+          <t>единица: fuel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mln conventional units, constant 2035 prices</t>
+          <t>т</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>unit:capacity</t>
+          <t>единица: money</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t/year</t>
+          <t>млн у.е., постоянные цены 2035 г.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>unit:reservation_rate</t>
+          <t>единица: capacity</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mln per (t/year)</t>
+          <t>т/год</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>unit:service_level</t>
+          <t>единица: reservation_rate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>share 0..1</t>
+          <t>млн у.е. за (т/год)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>unit:time_step</t>
+          <t>единица: service_level</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>calendar month</t>
+          <t>доля 0..1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sheets</t>
+          <t>единица: time_step</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>календарный месяц</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>периоды</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2035-01 … 2041-12, шаг — календарный месяц; подготовительный период до 2035-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>листы</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>yearly_balance</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>годовой баланс: спрос, выдача, дефицит, уровни сервиса, поступление, потери, запасы, 45-дневный резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>inventory_trace</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>помесячный материальный баланс и стоимость хранения</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>source_schedule</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>по источникам и годам: резерв, заказ, план/факт поставки, цена, оплачиваемый объём (take-or-pay), платежи</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>financial_breakdown</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>по годам: закупка, резервирование, хранение, постоянный OPEX, CAPEX, итого, PV, накопленный CAPEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>constraint_checks</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>нарушения: правило, строгость, год, месяц, источник, факт, лимит, превышение, сообщение</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>constraint_matrix</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>матрица проверок: каждое правило × год, включая выполненные</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>delivery_schedule</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>календарь поставок: месяц поставки, месяц размещения заказа, срок поставки, допустимость</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>kpi</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>итоговые показатели</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>investments</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>инвестиционные решения: даты опциона, реализации, ввода</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>assumptions</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>реестр допущений TEAM_ASSUMPTION: значение, единица, статус, диапазон, обоснование</t>
         </is>
       </c>
     </row>
@@ -774,7 +918,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>share per year (real)</t>
+          <t>доля в год (реальная ставка)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -789,7 +933,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Real discount rate for long-lived infrastructure with technology risk. Not given by the organizer. Used identically for all alternatives; sensitivity 0–12 % in experiments/run_sensitivity.py.
+          <t xml:space="preserve">Реальная ставка дисконтирования для долгоживущей инфраструктуры с технологическим риском. Организатором не задана. Применяется одинаково ко всем альтернативам; чувствительность 0–12 % в experiments/run_sensitivity.py.
 </t>
         </is>
       </c>
@@ -807,7 +951,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>год</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -822,7 +966,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year; PV factor = 1/(1+r)^(year-2035).</t>
+          <t>Годовые денежные потоки датируются началом каждого года; коэффициент приведения = 1/(1+r)^(год − 2035).</t>
         </is>
       </c>
     </row>
@@ -839,7 +983,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>enum start|mid|end</t>
+          <t>перечисление start|mid|end</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -854,7 +998,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year (exponent year-2035); mid/end-year conventions available and applied identically to all alternatives.</t>
+          <t>Момент внутри года, к которому отнесён годовой поток — начало (показатель степени год − 2035), середина (+0,5) или конец (+1); одинаково для всех альтернатив.</t>
         </is>
       </c>
     </row>
@@ -871,7 +1015,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -886,7 +1030,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Earliest order date of the preparatory period (Earth-Core needs 12 months before 2035-01).</t>
+          <t>Самая ранняя дата заказа в подготовительном периоде (Earth-Core требует 12 месяцев до 2035-01).</t>
         </is>
       </c>
     </row>
@@ -903,7 +1047,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>enum min|max|mean</t>
+          <t>перечисление min|max|mean</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -918,7 +1062,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Conservative end of the organizer lead-time ranges (Earth-New 24 months, ISRU 2 months).</t>
+          <t>Консервативный край диапазонов сроков поставки организатора (Earth-New 24 месяца, ISRU 2 месяца).</t>
         </is>
       </c>
     </row>
@@ -935,7 +1079,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>weeks</t>
+          <t>недель</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -950,7 +1094,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>365/12/7. Week lead times converted with ceil(weeks/4.345) -&gt; Emergency 6 weeks = 2 months.</t>
+          <t>365/12/7. Сроки в неделях переводятся как ceil(недели/4,345) -&gt; Emergency 6 недель = 2 месяца.</t>
         </is>
       </c>
     </row>
@@ -967,7 +1111,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>дней</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -982,7 +1126,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>365/12; day-denominated lead times converted with ceil.</t>
+          <t>365/12; сроки в днях переводятся с округлением вверх.</t>
         </is>
       </c>
     </row>
@@ -999,7 +1143,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1014,7 +1158,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Case gives no ZBO build time; modernization active from the CAPEX month. Varied in sensitivity.</t>
+          <t>Кейс не задаёт срок модернизации ZBO; она считается действующей с месяца оплаты CAPEX. Варьируется в анализе чувствительности.</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1175,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1046,7 +1190,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The 18–24 month Earth-New lead time is read as decision-to-first-delivery; orders are placed during preparation.</t>
+          <t>Срок Earth-New 18–24 месяца трактуется как время от решения до первой поставки; заказы размещаются в период подготовки, после ввода дополнительный срок заказа 0 месяцев.</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1207,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1078,7 +1222,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunar-ISRU available from 2038 once CAPEX is financed before 2038.</t>
+          <t>Lunar-ISRU доступен с 2038 года при финансировании CAPEX до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1239,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1110,7 +1254,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CAPEX 1250 must be financed before 2038.</t>
+          <t>CAPEX 1 250 млн должен быть профинансирован до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1271,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>map source_id -&gt; investment_id</t>
+          <t>отображение source_id -&gt; investment_id</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1142,7 +1286,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Earth-New capacity requires the exercised option; Lunar-ISRU requires the pilot CAPEX.</t>
+          <t>Мощность Earth-New требует реализованного опциона; Lunar-ISRU — CAPEX пилотного производства.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1303,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>map investment_id -&gt; storage_id</t>
+          <t>отображение investment_id -&gt; storage_id</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1174,7 +1318,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ZBO modernization switches the active storage mode (capacity 120 t, losses 1.2 %, OPEX 12/yr).</t>
+          <t>Модернизация ZBO переключает активный режим хранилища (ёмкость 120 т, потери 1,2 %, OPEX 12 млн/год).</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1335,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>share of annual total demand</t>
+          <t>доля годового общего спроса</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1206,7 +1350,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Emergency counts as the base channel in a year when its ordered volume exceeds 20 % of that year's demand.</t>
+          <t>Emergency считается базовым каналом в году, когда заказанный у него объём превышает 20 % спроса этого года.</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1367,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1238,7 +1382,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Average physical stock per month = (I_start + I_end)/2; holding = 0.72 x average x 1/12.</t>
+          <t>Средний физический запас за месяц = (I_start + I_end)/2; стоимость хранения = 0,72 × средний запас × 1/12.</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1399,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1270,7 +1414,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hard violation when end-of-month stock &gt; capacity; warning when stock after inflow (before withdrawals) &gt; capacity.</t>
+          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1431,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1302,7 +1446,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Contracted Emergency reserve counts only if stock covers demand during the 6-week lead time and reserved Emergency capacity &gt;= R_y.</t>
+          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1463,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1334,7 +1478,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>The preparatory-period purchase pays the source reservation rate on the purchased tonnage for one year; booked in 2035.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1495,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1366,7 +1510,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Holding cost charged from 2035-01; storage time in the preparatory period (&lt; 1 month) is not charged.</t>
+          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1527,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1398,7 +1542,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Organizer convention — uniform demand within the year, 365 days.</t>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
         </is>
       </c>
     </row>
@@ -13437,7 +13581,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -13450,7 +13594,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -13486,7 +13630,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -13499,7 +13643,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -13535,7 +13679,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -13548,7 +13692,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -13584,7 +13728,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I35" t="b">
@@ -13597,7 +13741,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -13633,7 +13777,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I36" t="b">
@@ -13646,7 +13790,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13826,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I37" t="b">
@@ -13695,7 +13839,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -13731,7 +13875,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I38" t="b">
@@ -13744,7 +13888,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -16384,7 +16528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M203"/>
+  <dimension ref="A1:N203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16453,6 +16597,11 @@
           <t>lead_time_ok</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>lead_time_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16508,6 +16657,11 @@
       <c r="M2" t="b">
         <v>1</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16563,6 +16717,11 @@
       <c r="M3" t="b">
         <v>1</v>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16618,6 +16777,11 @@
       <c r="M4" t="b">
         <v>1</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16673,6 +16837,11 @@
       <c r="M5" t="b">
         <v>1</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16728,6 +16897,11 @@
       <c r="M6" t="b">
         <v>1</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16783,6 +16957,11 @@
       <c r="M7" t="b">
         <v>1</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16838,6 +17017,11 @@
       <c r="M8" t="b">
         <v>1</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16893,6 +17077,11 @@
       <c r="M9" t="b">
         <v>1</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16948,6 +17137,11 @@
       <c r="M10" t="b">
         <v>1</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -17003,6 +17197,11 @@
       <c r="M11" t="b">
         <v>1</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17058,6 +17257,11 @@
       <c r="M12" t="b">
         <v>1</v>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17113,6 +17317,11 @@
       <c r="M13" t="b">
         <v>1</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17168,6 +17377,11 @@
       <c r="M14" t="b">
         <v>1</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17223,6 +17437,11 @@
       <c r="M15" t="b">
         <v>1</v>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -17278,6 +17497,11 @@
       <c r="M16" t="b">
         <v>1</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -17333,6 +17557,11 @@
       <c r="M17" t="b">
         <v>1</v>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17388,6 +17617,11 @@
       <c r="M18" t="b">
         <v>1</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17443,6 +17677,11 @@
       <c r="M19" t="b">
         <v>1</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -17498,6 +17737,11 @@
       <c r="M20" t="b">
         <v>1</v>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -17553,6 +17797,11 @@
       <c r="M21" t="b">
         <v>1</v>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -17608,6 +17857,11 @@
       <c r="M22" t="b">
         <v>1</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -17663,6 +17917,11 @@
       <c r="M23" t="b">
         <v>1</v>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -17718,6 +17977,11 @@
       <c r="M24" t="b">
         <v>1</v>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -17773,6 +18037,11 @@
       <c r="M25" t="b">
         <v>1</v>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -17828,6 +18097,11 @@
       <c r="M26" t="b">
         <v>1</v>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -17883,6 +18157,11 @@
       <c r="M27" t="b">
         <v>1</v>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -17938,6 +18217,11 @@
       <c r="M28" t="b">
         <v>1</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -17993,6 +18277,11 @@
       <c r="M29" t="b">
         <v>1</v>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -18048,6 +18337,11 @@
       <c r="M30" t="b">
         <v>1</v>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -18103,6 +18397,11 @@
       <c r="M31" t="b">
         <v>1</v>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -18158,6 +18457,11 @@
       <c r="M32" t="b">
         <v>1</v>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -18213,6 +18517,11 @@
       <c r="M33" t="b">
         <v>1</v>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -18268,6 +18577,11 @@
       <c r="M34" t="b">
         <v>1</v>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -18323,6 +18637,11 @@
       <c r="M35" t="b">
         <v>1</v>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -18378,6 +18697,11 @@
       <c r="M36" t="b">
         <v>1</v>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -18433,6 +18757,11 @@
       <c r="M37" t="b">
         <v>1</v>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -18488,6 +18817,11 @@
       <c r="M38" t="b">
         <v>1</v>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -18543,6 +18877,11 @@
       <c r="M39" t="b">
         <v>1</v>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -18598,6 +18937,11 @@
       <c r="M40" t="b">
         <v>1</v>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -18653,6 +18997,11 @@
       <c r="M41" t="b">
         <v>1</v>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -18708,6 +19057,11 @@
       <c r="M42" t="b">
         <v>1</v>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -18763,6 +19117,11 @@
       <c r="M43" t="b">
         <v>1</v>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -18818,6 +19177,11 @@
       <c r="M44" t="b">
         <v>1</v>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -18873,6 +19237,11 @@
       <c r="M45" t="b">
         <v>1</v>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -18928,6 +19297,11 @@
       <c r="M46" t="b">
         <v>1</v>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -18983,6 +19357,11 @@
       <c r="M47" t="b">
         <v>1</v>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -19038,6 +19417,11 @@
       <c r="M48" t="b">
         <v>1</v>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -19093,6 +19477,11 @@
       <c r="M49" t="b">
         <v>1</v>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -19148,6 +19537,11 @@
       <c r="M50" t="b">
         <v>1</v>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -19203,6 +19597,11 @@
       <c r="M51" t="b">
         <v>1</v>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -19258,6 +19657,11 @@
       <c r="M52" t="b">
         <v>1</v>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -19313,6 +19717,11 @@
       <c r="M53" t="b">
         <v>1</v>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -19368,6 +19777,11 @@
       <c r="M54" t="b">
         <v>1</v>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -19423,6 +19837,11 @@
       <c r="M55" t="b">
         <v>1</v>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -19478,6 +19897,11 @@
       <c r="M56" t="b">
         <v>1</v>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -19533,6 +19957,11 @@
       <c r="M57" t="b">
         <v>1</v>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -19588,6 +20017,11 @@
       <c r="M58" t="b">
         <v>1</v>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -19643,6 +20077,11 @@
       <c r="M59" t="b">
         <v>1</v>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -19698,6 +20137,11 @@
       <c r="M60" t="b">
         <v>1</v>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -19753,6 +20197,11 @@
       <c r="M61" t="b">
         <v>1</v>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -19808,6 +20257,11 @@
       <c r="M62" t="b">
         <v>1</v>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -19863,6 +20317,11 @@
       <c r="M63" t="b">
         <v>1</v>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -19918,6 +20377,11 @@
       <c r="M64" t="b">
         <v>1</v>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -19973,6 +20437,11 @@
       <c r="M65" t="b">
         <v>1</v>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -20028,6 +20497,11 @@
       <c r="M66" t="b">
         <v>1</v>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -20083,6 +20557,11 @@
       <c r="M67" t="b">
         <v>1</v>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -20138,6 +20617,11 @@
       <c r="M68" t="b">
         <v>1</v>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -20193,6 +20677,11 @@
       <c r="M69" t="b">
         <v>1</v>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -20248,6 +20737,11 @@
       <c r="M70" t="b">
         <v>1</v>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -20303,6 +20797,11 @@
       <c r="M71" t="b">
         <v>1</v>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -20358,6 +20857,11 @@
       <c r="M72" t="b">
         <v>1</v>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -20413,6 +20917,11 @@
       <c r="M73" t="b">
         <v>1</v>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -20468,6 +20977,11 @@
       <c r="M74" t="b">
         <v>1</v>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -20523,6 +21037,11 @@
       <c r="M75" t="b">
         <v>1</v>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -20578,6 +21097,11 @@
       <c r="M76" t="b">
         <v>1</v>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -20633,6 +21157,11 @@
       <c r="M77" t="b">
         <v>1</v>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -20688,6 +21217,11 @@
       <c r="M78" t="b">
         <v>1</v>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -20743,6 +21277,11 @@
       <c r="M79" t="b">
         <v>1</v>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -20798,6 +21337,11 @@
       <c r="M80" t="b">
         <v>1</v>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -20853,6 +21397,11 @@
       <c r="M81" t="b">
         <v>1</v>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -20908,6 +21457,11 @@
       <c r="M82" t="b">
         <v>1</v>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -20963,6 +21517,11 @@
       <c r="M83" t="b">
         <v>1</v>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -21018,6 +21577,11 @@
       <c r="M84" t="b">
         <v>1</v>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -21073,6 +21637,11 @@
       <c r="M85" t="b">
         <v>1</v>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -21128,6 +21697,11 @@
       <c r="M86" t="b">
         <v>1</v>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -21183,6 +21757,11 @@
       <c r="M87" t="b">
         <v>1</v>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -21238,6 +21817,11 @@
       <c r="M88" t="b">
         <v>1</v>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -21293,6 +21877,11 @@
       <c r="M89" t="b">
         <v>1</v>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -21348,6 +21937,11 @@
       <c r="M90" t="b">
         <v>1</v>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -21403,6 +21997,11 @@
       <c r="M91" t="b">
         <v>1</v>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -21458,6 +22057,11 @@
       <c r="M92" t="b">
         <v>1</v>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -21513,6 +22117,11 @@
       <c r="M93" t="b">
         <v>1</v>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -21568,6 +22177,11 @@
       <c r="M94" t="b">
         <v>1</v>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -21623,6 +22237,11 @@
       <c r="M95" t="b">
         <v>1</v>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -21678,6 +22297,11 @@
       <c r="M96" t="b">
         <v>1</v>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -21733,6 +22357,11 @@
       <c r="M97" t="b">
         <v>1</v>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -21788,6 +22417,11 @@
       <c r="M98" t="b">
         <v>1</v>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -21843,6 +22477,11 @@
       <c r="M99" t="b">
         <v>1</v>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -21898,6 +22537,11 @@
       <c r="M100" t="b">
         <v>1</v>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -21953,6 +22597,11 @@
       <c r="M101" t="b">
         <v>1</v>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -22008,6 +22657,11 @@
       <c r="M102" t="b">
         <v>1</v>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -22063,6 +22717,11 @@
       <c r="M103" t="b">
         <v>1</v>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -22118,6 +22777,11 @@
       <c r="M104" t="b">
         <v>1</v>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -22173,6 +22837,11 @@
       <c r="M105" t="b">
         <v>1</v>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -22228,6 +22897,11 @@
       <c r="M106" t="b">
         <v>1</v>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -22283,6 +22957,11 @@
       <c r="M107" t="b">
         <v>1</v>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -22338,6 +23017,11 @@
       <c r="M108" t="b">
         <v>1</v>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -22393,6 +23077,11 @@
       <c r="M109" t="b">
         <v>1</v>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -22448,6 +23137,11 @@
       <c r="M110" t="b">
         <v>1</v>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -22503,6 +23197,11 @@
       <c r="M111" t="b">
         <v>1</v>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -22558,6 +23257,11 @@
       <c r="M112" t="b">
         <v>1</v>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -22613,6 +23317,11 @@
       <c r="M113" t="b">
         <v>1</v>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -22668,6 +23377,11 @@
       <c r="M114" t="b">
         <v>1</v>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -22723,6 +23437,11 @@
       <c r="M115" t="b">
         <v>1</v>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -22778,6 +23497,11 @@
       <c r="M116" t="b">
         <v>1</v>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -22833,6 +23557,11 @@
       <c r="M117" t="b">
         <v>1</v>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -22888,6 +23617,11 @@
       <c r="M118" t="b">
         <v>1</v>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -22943,6 +23677,11 @@
       <c r="M119" t="b">
         <v>1</v>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -22998,6 +23737,11 @@
       <c r="M120" t="b">
         <v>1</v>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -23053,6 +23797,11 @@
       <c r="M121" t="b">
         <v>1</v>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -23108,6 +23857,11 @@
       <c r="M122" t="b">
         <v>1</v>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -23163,6 +23917,11 @@
       <c r="M123" t="b">
         <v>1</v>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -23218,6 +23977,11 @@
       <c r="M124" t="b">
         <v>1</v>
       </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -23273,6 +24037,11 @@
       <c r="M125" t="b">
         <v>1</v>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -23328,6 +24097,11 @@
       <c r="M126" t="b">
         <v>1</v>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -23383,6 +24157,11 @@
       <c r="M127" t="b">
         <v>1</v>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -23438,6 +24217,11 @@
       <c r="M128" t="b">
         <v>1</v>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -23493,6 +24277,11 @@
       <c r="M129" t="b">
         <v>1</v>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -23548,6 +24337,11 @@
       <c r="M130" t="b">
         <v>1</v>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -23603,6 +24397,11 @@
       <c r="M131" t="b">
         <v>1</v>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -23658,6 +24457,11 @@
       <c r="M132" t="b">
         <v>1</v>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -23713,6 +24517,11 @@
       <c r="M133" t="b">
         <v>1</v>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -23768,6 +24577,11 @@
       <c r="M134" t="b">
         <v>1</v>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -23823,6 +24637,11 @@
       <c r="M135" t="b">
         <v>1</v>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -23878,6 +24697,11 @@
       <c r="M136" t="b">
         <v>1</v>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -23933,6 +24757,11 @@
       <c r="M137" t="b">
         <v>1</v>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -23988,6 +24817,11 @@
       <c r="M138" t="b">
         <v>1</v>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -24043,6 +24877,11 @@
       <c r="M139" t="b">
         <v>1</v>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -24098,6 +24937,11 @@
       <c r="M140" t="b">
         <v>1</v>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -24153,6 +24997,11 @@
       <c r="M141" t="b">
         <v>1</v>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -24208,6 +25057,11 @@
       <c r="M142" t="b">
         <v>1</v>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -24263,6 +25117,11 @@
       <c r="M143" t="b">
         <v>1</v>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -24318,6 +25177,11 @@
       <c r="M144" t="b">
         <v>1</v>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -24373,6 +25237,11 @@
       <c r="M145" t="b">
         <v>1</v>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -24428,6 +25297,11 @@
       <c r="M146" t="b">
         <v>1</v>
       </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -24483,6 +25357,11 @@
       <c r="M147" t="b">
         <v>1</v>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -24538,6 +25417,11 @@
       <c r="M148" t="b">
         <v>1</v>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -24593,6 +25477,11 @@
       <c r="M149" t="b">
         <v>1</v>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -24648,6 +25537,11 @@
       <c r="M150" t="b">
         <v>1</v>
       </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -24703,6 +25597,11 @@
       <c r="M151" t="b">
         <v>1</v>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -24758,6 +25657,11 @@
       <c r="M152" t="b">
         <v>1</v>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -24813,6 +25717,11 @@
       <c r="M153" t="b">
         <v>1</v>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -24868,6 +25777,11 @@
       <c r="M154" t="b">
         <v>1</v>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -24923,6 +25837,11 @@
       <c r="M155" t="b">
         <v>1</v>
       </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -24978,6 +25897,11 @@
       <c r="M156" t="b">
         <v>1</v>
       </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -25033,6 +25957,11 @@
       <c r="M157" t="b">
         <v>1</v>
       </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -25088,6 +26017,11 @@
       <c r="M158" t="b">
         <v>1</v>
       </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -25143,6 +26077,11 @@
       <c r="M159" t="b">
         <v>1</v>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -25198,6 +26137,11 @@
       <c r="M160" t="b">
         <v>1</v>
       </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -25253,6 +26197,11 @@
       <c r="M161" t="b">
         <v>1</v>
       </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -25308,6 +26257,11 @@
       <c r="M162" t="b">
         <v>1</v>
       </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -25363,6 +26317,11 @@
       <c r="M163" t="b">
         <v>1</v>
       </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -25418,6 +26377,11 @@
       <c r="M164" t="b">
         <v>1</v>
       </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -25473,6 +26437,11 @@
       <c r="M165" t="b">
         <v>1</v>
       </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -25528,6 +26497,11 @@
       <c r="M166" t="b">
         <v>1</v>
       </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -25583,6 +26557,11 @@
       <c r="M167" t="b">
         <v>1</v>
       </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -25638,6 +26617,11 @@
       <c r="M168" t="b">
         <v>1</v>
       </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -25693,6 +26677,11 @@
       <c r="M169" t="b">
         <v>1</v>
       </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -25748,6 +26737,11 @@
       <c r="M170" t="b">
         <v>1</v>
       </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -25803,6 +26797,11 @@
       <c r="M171" t="b">
         <v>1</v>
       </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -25858,6 +26857,11 @@
       <c r="M172" t="b">
         <v>1</v>
       </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -25913,6 +26917,11 @@
       <c r="M173" t="b">
         <v>1</v>
       </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -25968,6 +26977,11 @@
       <c r="M174" t="b">
         <v>1</v>
       </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -26023,6 +27037,11 @@
       <c r="M175" t="b">
         <v>1</v>
       </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -26078,6 +27097,11 @@
       <c r="M176" t="b">
         <v>1</v>
       </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -26133,6 +27157,11 @@
       <c r="M177" t="b">
         <v>1</v>
       </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -26188,6 +27217,11 @@
       <c r="M178" t="b">
         <v>1</v>
       </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -26243,6 +27277,11 @@
       <c r="M179" t="b">
         <v>1</v>
       </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -26298,6 +27337,11 @@
       <c r="M180" t="b">
         <v>1</v>
       </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -26353,6 +27397,11 @@
       <c r="M181" t="b">
         <v>1</v>
       </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -26408,6 +27457,11 @@
       <c r="M182" t="b">
         <v>1</v>
       </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -26463,6 +27517,11 @@
       <c r="M183" t="b">
         <v>1</v>
       </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -26518,6 +27577,11 @@
       <c r="M184" t="b">
         <v>1</v>
       </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -26573,6 +27637,11 @@
       <c r="M185" t="b">
         <v>1</v>
       </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -26628,6 +27697,11 @@
       <c r="M186" t="b">
         <v>1</v>
       </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -26683,6 +27757,11 @@
       <c r="M187" t="b">
         <v>1</v>
       </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -26738,6 +27817,11 @@
       <c r="M188" t="b">
         <v>1</v>
       </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -26793,6 +27877,11 @@
       <c r="M189" t="b">
         <v>1</v>
       </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -26848,6 +27937,11 @@
       <c r="M190" t="b">
         <v>1</v>
       </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -26903,6 +27997,11 @@
       <c r="M191" t="b">
         <v>1</v>
       </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -26958,6 +28057,11 @@
       <c r="M192" t="b">
         <v>1</v>
       </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -27013,6 +28117,11 @@
       <c r="M193" t="b">
         <v>1</v>
       </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -27068,6 +28177,11 @@
       <c r="M194" t="b">
         <v>1</v>
       </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -27123,6 +28237,11 @@
       <c r="M195" t="b">
         <v>1</v>
       </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -27178,6 +28297,11 @@
       <c r="M196" t="b">
         <v>1</v>
       </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -27233,6 +28357,11 @@
       <c r="M197" t="b">
         <v>1</v>
       </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -27288,6 +28417,11 @@
       <c r="M198" t="b">
         <v>1</v>
       </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -27343,6 +28477,11 @@
       <c r="M199" t="b">
         <v>1</v>
       </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -27398,6 +28537,11 @@
       <c r="M200" t="b">
         <v>1</v>
       </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -27453,6 +28597,11 @@
       <c r="M201" t="b">
         <v>1</v>
       </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -27508,6 +28657,11 @@
       <c r="M202" t="b">
         <v>1</v>
       </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -27562,6 +28716,11 @@
       </c>
       <c r="M203" t="b">
         <v>1</v>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>срок поставки 3 мес.; заказы с 2034-01</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/results/extensibility/run/results.xlsx
+++ b/results/extensibility/run/results.xlsx
@@ -870,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1543,6 +1543,39 @@
       <c r="F21" t="inlineStr">
         <is>
           <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>undelivered_volume_paid</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>логическое</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>[true, false]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
         </is>
       </c>
     </row>
@@ -13570,18 +13603,18 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -13594,7 +13627,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -13619,18 +13652,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -13643,7 +13676,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -13668,18 +13701,18 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -13692,7 +13725,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -13717,18 +13750,18 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I35" t="b">
@@ -13741,7 +13774,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -13766,18 +13799,18 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I36" t="b">
@@ -13790,7 +13823,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -13815,18 +13848,18 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I37" t="b">
@@ -13839,7 +13872,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -13864,18 +13897,18 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I38" t="b">
@@ -13888,7 +13921,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -13913,7 +13946,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -13937,7 +13970,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2035-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14148,7 +14181,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -14172,7 +14205,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14383,11 +14416,11 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>30.82224430000005</v>
+        <v>25.44727350000007</v>
       </c>
       <c r="G49" t="n">
         <v>70</v>
@@ -14407,7 +14440,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14716,7 +14749,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -14740,7 +14773,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2038-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15082,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -15073,7 +15106,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2039-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -15480,7 +15513,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -15504,7 +15537,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2040-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -16009,7 +16042,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -16033,7 +16066,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2041-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>

--- a/results/extensibility/run/results.xlsx
+++ b/results/extensibility/run/results.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -870,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1575,6 +1575,105 @@
       <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>exp10_demand_max</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>дополнительный относительный рост спроса</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>exp10_isru_reduction_max</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>exp10_price_half_range</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>относительное отклонение переменной цены от обязательного стресса</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>[-0.1, 0.1]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
         </is>
       </c>

--- a/results/extensibility/run/results.xlsx
+++ b/results/extensibility/run/results.xlsx
@@ -8470,7 +8470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U44"/>
+  <dimension ref="A1:V44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8579,6 +8579,11 @@
           <t>reservation_payment_mln</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8654,6 +8659,9 @@
       <c r="U2" t="n">
         <v>1.93647</v>
       </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8729,6 +8737,9 @@
       <c r="U3" t="n">
         <v>49.4442</v>
       </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8804,6 +8815,9 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8879,6 +8893,9 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8954,6 +8971,9 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9029,6 +9049,9 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9104,6 +9127,9 @@
       <c r="U8" t="n">
         <v>0</v>
       </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9179,6 +9205,9 @@
       <c r="U9" t="n">
         <v>68.8734</v>
       </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9254,6 +9283,9 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9329,6 +9361,9 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9404,6 +9439,9 @@
       <c r="U12" t="n">
         <v>0</v>
       </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9479,6 +9517,9 @@
       <c r="U13" t="n">
         <v>0</v>
       </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9554,6 +9595,9 @@
       <c r="U14" t="n">
         <v>0</v>
       </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9629,6 +9673,9 @@
       <c r="U15" t="n">
         <v>85.5</v>
       </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9704,6 +9751,9 @@
       <c r="U16" t="n">
         <v>1.97835</v>
       </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9779,6 +9829,9 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9854,6 +9907,9 @@
       <c r="U18" t="n">
         <v>0</v>
       </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9929,6 +9985,9 @@
       <c r="U19" t="n">
         <v>0</v>
       </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10004,6 +10063,9 @@
       <c r="U20" t="n">
         <v>0</v>
       </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -10079,6 +10141,9 @@
       <c r="U21" t="n">
         <v>72.7974</v>
       </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10154,6 +10219,9 @@
       <c r="U22" t="n">
         <v>0</v>
       </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -10229,6 +10297,9 @@
       <c r="U23" t="n">
         <v>0</v>
       </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -10304,6 +10375,9 @@
       <c r="U24" t="n">
         <v>0</v>
       </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -10379,6 +10453,9 @@
       <c r="U25" t="n">
         <v>0</v>
       </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -10454,6 +10531,9 @@
       <c r="U26" t="n">
         <v>0</v>
       </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -10529,6 +10609,9 @@
       <c r="U27" t="n">
         <v>68.6799</v>
       </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -10604,6 +10687,9 @@
       <c r="U28" t="n">
         <v>0</v>
       </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -10679,6 +10765,9 @@
       <c r="U29" t="n">
         <v>0</v>
       </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -10754,6 +10843,9 @@
       <c r="U30" t="n">
         <v>0</v>
       </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -10829,6 +10921,9 @@
       <c r="U31" t="n">
         <v>0</v>
       </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -10904,6 +10999,9 @@
       <c r="U32" t="n">
         <v>12</v>
       </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -10979,6 +11077,9 @@
       <c r="U33" t="n">
         <v>85.5</v>
       </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -11054,6 +11155,9 @@
       <c r="U34" t="n">
         <v>4.8336</v>
       </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -11129,6 +11233,9 @@
       <c r="U35" t="n">
         <v>0</v>
       </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -11204,6 +11311,9 @@
       <c r="U36" t="n">
         <v>0</v>
       </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -11279,6 +11389,9 @@
       <c r="U37" t="n">
         <v>0</v>
       </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -11354,6 +11467,9 @@
       <c r="U38" t="n">
         <v>12</v>
       </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -11429,6 +11545,9 @@
       <c r="U39" t="n">
         <v>85.5</v>
       </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -11504,6 +11623,9 @@
       <c r="U40" t="n">
         <v>12.8199</v>
       </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -11579,6 +11701,9 @@
       <c r="U41" t="n">
         <v>0</v>
       </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -11654,6 +11779,9 @@
       <c r="U42" t="n">
         <v>0</v>
       </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -11729,6 +11857,9 @@
       <c r="U43" t="n">
         <v>0</v>
       </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -11803,6 +11934,9 @@
       </c>
       <c r="U44" t="n">
         <v>12</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -11816,7 +11950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11880,6 +12014,11 @@
           <t>cumulative_capex_mln</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11922,6 +12061,9 @@
       <c r="L2" t="n">
         <v>0</v>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11964,6 +12106,9 @@
       <c r="L3" t="n">
         <v>1250</v>
       </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12006,6 +12151,9 @@
       <c r="L4" t="n">
         <v>1430</v>
       </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12048,6 +12196,9 @@
       <c r="L5" t="n">
         <v>1430</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12090,6 +12241,9 @@
       <c r="L6" t="n">
         <v>1430</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12132,6 +12286,9 @@
       <c r="L7" t="n">
         <v>1430</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12173,6 +12330,9 @@
       </c>
       <c r="L8" t="n">
         <v>1430</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -28866,7 +29026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29304,11 +29464,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>opening_inventory_t</t>
+          <t>take_or_pay_topup_mln</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.328859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -29324,11 +29484,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>closing_inventory_t</t>
+          <t>opening_inventory_t</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>55.4798531000002</v>
+        <v>12.328859</v>
       </c>
     </row>
     <row r="24">
@@ -29344,11 +29504,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>closing_inventory_t</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>55.4798531000002</v>
       </c>
     </row>
     <row r="25">
@@ -29364,7 +29524,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -29384,7 +29544,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>guideline_violations</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -29404,11 +29564,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D27" t="b">
-        <v>1</v>
+          <t>warnings</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -29424,11 +29584,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>checks_total</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>92</v>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -29444,10 +29604,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D30" t="n">
         <v>92</v>
       </c>
     </row>

--- a/results/extensibility/run/results.xlsx
+++ b/results/extensibility/run/results.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="preparatory_period" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="contract_reserve_proof" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -578,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions, preparatory_period, contract_reserve_proof</t>
         </is>
       </c>
     </row>
@@ -870,7 +872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1394,7 +1396,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>"end_of_month_hard_peak_warning"</t>
+          <t>"end_of_month_and_intra_month_peak_hard"</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1414,24 +1416,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
+          <t>Оба превышения ёмкости — жёсткие нарушения. Проверяется запас на конец месяца и расчётный пик внутри месяца при заявленном дроблении поставок (intra_month_delivery_batches): физическая исполнимость плана доказывается графиком поступлений, а не пометкой допущения.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>emergency_reserve_equivalence</t>
+          <t>intra_month_delivery_batches</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"stock_covers_lead_time_and_reserved_capacity_covers_45d"</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>правило</t>
+          <t>партий в месяц</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1441,29 +1443,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>[1, 4]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
+          <t>Месячный объём канала приходит N равными партиями, равномерно распределёнными по месяцу, при равномерной выдаче потребителям (конвенция организатора). Пик запаса после партии j равен I_нач + (j·нетто − (j−1)·выдача)/N, максимум берётся по j = 1..N. При N = 1 это запас сразу после единственного поступления, до выдачи, — консервативный край без допущения о внутримесячной синхронизации поставок и выдачи. При N → ∞ пик стремится к max(запас на начало, запас на конец). Выбрано N = 1: организатор не задаёт размер отдельной партии, и ни один принятый план команды не нуждается в дроблении. Чувствительность к N = 2 и N = 4 показана в results/intra_month/intra_month_capacity.md.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>opening_stock_reservation_years</t>
+          <t>emergency_reserve_equivalence</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>"contracted_batch_schedule_and_waiting_cover"</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>лет</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1473,29 +1475,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[0.0, 1.0]</t>
+          <t>null</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
+          <t>Договорный аварийный резерв засчитывается только при одновременном выполнении пяти условий, каждое из которых печатается отдельной строкой в contract_reserve_proof: (1) канал доступен в этом году; (2) договорный срок исполнения партии не быстрее срока поставки канала по данным организатора; (3) нетто-объём гарантированной партии после потерь хранилища &gt;= R_y; (4) зарезервированная мощность канала за вычетом обычных заказов года &gt;= партия × число активаций; (5) физический запас на начало года покрывает спрос за время активации плюс срок исполнения. Сам по себе лимит мощности канала (80 т/год) эквивалентности не доказывает. Если блок inventory_policy.emergency_contract не задан, эквивалентность не доказана и действует физический резерв. Правило следует кейсу, §«Начальный запас и резерв».</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>prep_period_holding_charged</t>
+          <t>opening_stock_reservation_years</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>логическое</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1505,176 +1507,319 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[true, false]</t>
+          <t>[0.0, 1.0]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>intra_year_demand_profile</t>
+          <t>prep_period_holding_charged</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"uniform"</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>перечисление</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CASE_INPUT</t>
+          <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>["uniform"]</t>
+          <t>[true, false]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+          <t>Хранение начального запаса начисляется с фактического месяца поставки, а не с 2035-01: ранняя поставка начального запаса не хранится бесплатно. Правило то же, что и в основном периоде (трапеция): в месяц поставки средний запас равен половине поступления, в каждый последующий месяц подготовительного периода — полному нетто-запасу. Расход относится на первый финансовый год (2035), как закупка и плата за резерв подготовительного периода. Значение false выключает начисление и оставлено только для сопоставления с прежней версией расчёта.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>intra_year_demand_profile</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>"uniform"</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>перечисление</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>["uniform"]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>undelivered_volume_paid</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>логическое</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>CASE_INPUT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>[true, false]</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
 </t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>exp10_demand_max</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>дополнительный относительный рост спроса</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
 </t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>exp10_isru_reduction_max</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
 </t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>exp10_price_half_range</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>относительное отклонение переменной цены от обязательного стресса</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>[-0.1, 0.1]</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>storage_mode</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>opening_t</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>arrived_t</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>closing_t</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>holding_cost_mln</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2034-12</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.36986577</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>(empty)</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U85"/>
+  <dimension ref="A1:W85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2491,6 +2636,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>peak_stock_t</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>delivery_batches</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>inflow_A_t</t>
         </is>
       </c>
@@ -2563,6 +2718,12 @@
         <v>0.7520604900000002</v>
       </c>
       <c r="U2" t="n">
+        <v>21.07315733333333</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2634,6 +2795,12 @@
         <v>0.7767183900000002</v>
       </c>
       <c r="U3" t="n">
+        <v>21.48412233333334</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2705,6 +2872,12 @@
         <v>0.8013762900000003</v>
       </c>
       <c r="U4" t="n">
+        <v>21.89508733333334</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2776,6 +2949,12 @@
         <v>0.8260341900000004</v>
       </c>
       <c r="U5" t="n">
+        <v>22.30605233333334</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2847,6 +3026,12 @@
         <v>0.8506920900000003</v>
       </c>
       <c r="U6" t="n">
+        <v>22.71701733333334</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2918,6 +3103,12 @@
         <v>0.8753499900000005</v>
       </c>
       <c r="U7" t="n">
+        <v>23.12798233333334</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2989,6 +3180,12 @@
         <v>0.9000078900000005</v>
       </c>
       <c r="U8" t="n">
+        <v>23.53894733333334</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3060,6 +3257,12 @@
         <v>0.9246657900000006</v>
       </c>
       <c r="U9" t="n">
+        <v>23.94991233333334</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3131,6 +3334,12 @@
         <v>0.9493236900000007</v>
       </c>
       <c r="U10" t="n">
+        <v>24.36087733333335</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3202,6 +3411,12 @@
         <v>0.973981590000001</v>
       </c>
       <c r="U11" t="n">
+        <v>24.77184233333335</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3273,6 +3488,12 @@
         <v>0.9986394900000012</v>
       </c>
       <c r="U12" t="n">
+        <v>25.18280733333335</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3344,6 +3565,12 @@
         <v>1.023297390000001</v>
       </c>
       <c r="U13" t="n">
+        <v>25.59377233333336</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3415,6 +3642,12 @@
         <v>1.051037512500002</v>
       </c>
       <c r="U14" t="n">
+        <v>29.44081141666669</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3486,6 +3719,12 @@
         <v>1.081859857500002</v>
       </c>
       <c r="U15" t="n">
+        <v>29.95451716666669</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3557,6 +3796,12 @@
         <v>1.112682202500001</v>
       </c>
       <c r="U16" t="n">
+        <v>30.46822291666669</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3628,6 +3873,12 @@
         <v>1.143504547500002</v>
       </c>
       <c r="U17" t="n">
+        <v>30.98192866666669</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3699,6 +3950,12 @@
         <v>1.174326892500001</v>
       </c>
       <c r="U18" t="n">
+        <v>31.49563441666669</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3770,6 +4027,12 @@
         <v>1.205149237500002</v>
       </c>
       <c r="U19" t="n">
+        <v>32.00934016666669</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3841,6 +4104,12 @@
         <v>1.235971582500002</v>
       </c>
       <c r="U20" t="n">
+        <v>32.5230459166667</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3912,6 +4181,12 @@
         <v>1.266793927500003</v>
       </c>
       <c r="U21" t="n">
+        <v>33.0367516666667</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3983,6 +4258,12 @@
         <v>1.297616272500003</v>
       </c>
       <c r="U22" t="n">
+        <v>33.55045741666671</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4054,6 +4335,12 @@
         <v>1.328438617500003</v>
       </c>
       <c r="U23" t="n">
+        <v>34.06416316666672</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4125,6 +4412,12 @@
         <v>1.359260962500004</v>
       </c>
       <c r="U24" t="n">
+        <v>34.57786891666672</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4196,6 +4489,12 @@
         <v>1.390083307500004</v>
       </c>
       <c r="U25" t="n">
+        <v>35.09157466666673</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4267,6 +4566,12 @@
         <v>1.415606307500004</v>
       </c>
       <c r="U26" t="n">
+        <v>39.59530225000007</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4338,6 +4643,12 @@
         <v>1.435829962500004</v>
       </c>
       <c r="U27" t="n">
+        <v>39.93236316666674</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4409,6 +4720,12 @@
         <v>1.456053617500004</v>
       </c>
       <c r="U28" t="n">
+        <v>40.2694240833334</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4480,6 +4797,12 @@
         <v>1.476277272500004</v>
       </c>
       <c r="U29" t="n">
+        <v>40.60648500000007</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4551,6 +4874,12 @@
         <v>1.496500927500004</v>
       </c>
       <c r="U30" t="n">
+        <v>40.94354591666674</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4622,6 +4951,12 @@
         <v>1.516724582500004</v>
       </c>
       <c r="U31" t="n">
+        <v>41.2806068333334</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4693,6 +5028,12 @@
         <v>1.553711264000004</v>
       </c>
       <c r="U32" t="n">
+        <v>42.17643530000007</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4764,6 +5105,12 @@
         <v>1.607460972000004</v>
       </c>
       <c r="U33" t="n">
+        <v>43.07226376666673</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4835,6 +5182,12 @@
         <v>1.661210680000003</v>
       </c>
       <c r="U34" t="n">
+        <v>43.96809223333339</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4906,6 +5259,12 @@
         <v>1.714960388000003</v>
       </c>
       <c r="U35" t="n">
+        <v>44.86392070000006</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4977,6 +5336,12 @@
         <v>1.768710096000003</v>
       </c>
       <c r="U36" t="n">
+        <v>45.75974916666672</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5048,6 +5413,12 @@
         <v>1.822459804000003</v>
       </c>
       <c r="U37" t="n">
+        <v>46.65557763333339</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5119,6 +5490,12 @@
         <v>1.623910016000003</v>
       </c>
       <c r="U38" t="n">
+        <v>44.14142290000005</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5190,6 +5567,12 @@
         <v>1.173060732000003</v>
       </c>
       <c r="U39" t="n">
+        <v>36.62726816666672</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5261,6 +5644,12 @@
         <v>1.018611448000003</v>
       </c>
       <c r="U40" t="n">
+        <v>38.99311343333338</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5332,6 +5721,12 @@
         <v>1.160562164000004</v>
       </c>
       <c r="U41" t="n">
+        <v>41.35895870000006</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5403,6 +5798,12 @@
         <v>1.302512880000004</v>
       </c>
       <c r="U42" t="n">
+        <v>43.72480396666673</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5474,6 +5875,12 @@
         <v>1.444463596000004</v>
       </c>
       <c r="U43" t="n">
+        <v>46.09064923333339</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5545,6 +5952,12 @@
         <v>1.586414312000004</v>
       </c>
       <c r="U44" t="n">
+        <v>48.45649450000006</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5616,6 +6029,12 @@
         <v>1.728365028000004</v>
       </c>
       <c r="U45" t="n">
+        <v>50.82233976666673</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5687,6 +6106,12 @@
         <v>1.870315744000004</v>
       </c>
       <c r="U46" t="n">
+        <v>53.1881850333334</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5758,6 +6183,12 @@
         <v>2.012266460000004</v>
       </c>
       <c r="U47" t="n">
+        <v>55.55403030000006</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5829,6 +6260,12 @@
         <v>2.154217176000004</v>
       </c>
       <c r="U48" t="n">
+        <v>57.91987556666673</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5900,6 +6337,12 @@
         <v>2.296167892000004</v>
       </c>
       <c r="U49" t="n">
+        <v>60.2857208333334</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5971,6 +6414,12 @@
         <v>2.388718602000004</v>
       </c>
       <c r="U50" t="n">
+        <v>66.83823256666673</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="W50" t="n">
         <v>12.71846666666667</v>
       </c>
     </row>
@@ -6042,6 +6491,12 @@
         <v>2.431869306000004</v>
       </c>
       <c r="U51" t="n">
+        <v>67.55741096666674</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
         <v>12.71846666666667</v>
       </c>
     </row>
@@ -6113,6 +6568,12 @@
         <v>2.475020010000005</v>
       </c>
       <c r="U52" t="n">
+        <v>68.27658936666674</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" t="n">
         <v>12.71846666666667</v>
       </c>
     </row>
@@ -6184,6 +6645,12 @@
         <v>2.518170714000005</v>
       </c>
       <c r="U53" t="n">
+        <v>68.99576776666675</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="n">
         <v>12.71846666666667</v>
       </c>
     </row>
@@ -6255,6 +6722,12 @@
         <v>2.561321418000005</v>
       </c>
       <c r="U54" t="n">
+        <v>69.71494616666675</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="n">
         <v>12.71846666666667</v>
       </c>
     </row>
@@ -6326,6 +6799,12 @@
         <v>2.604472122000006</v>
       </c>
       <c r="U55" t="n">
+        <v>70.43412456666675</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
         <v>12.71846666666667</v>
       </c>
     </row>
@@ -6397,6 +6876,12 @@
         <v>2.647622826000006</v>
       </c>
       <c r="U56" t="n">
+        <v>71.15330296666676</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="n">
         <v>12.71846666666667</v>
       </c>
     </row>
@@ -6468,6 +6953,12 @@
         <v>2.690773530000006</v>
       </c>
       <c r="U57" t="n">
+        <v>71.87248136666676</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
         <v>12.71846666666667</v>
       </c>
     </row>
@@ -6539,6 +7030,12 @@
         <v>2.733924234000007</v>
       </c>
       <c r="U58" t="n">
+        <v>72.59165976666677</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="n">
         <v>12.71846666666667</v>
       </c>
     </row>
@@ -6610,6 +7107,12 @@
         <v>2.777074938000007</v>
       </c>
       <c r="U59" t="n">
+        <v>73.31083816666677</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1</v>
+      </c>
+      <c r="W59" t="n">
         <v>12.71846666666667</v>
       </c>
     </row>
@@ -6681,6 +7184,12 @@
         <v>2.820225642000007</v>
       </c>
       <c r="U60" t="n">
+        <v>74.03001656666677</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" t="n">
         <v>12.71846666666667</v>
       </c>
     </row>
@@ -6752,6 +7261,12 @@
         <v>2.863376346000007</v>
       </c>
       <c r="U61" t="n">
+        <v>74.74919496666678</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
+      <c r="W61" t="n">
         <v>12.71846666666667</v>
       </c>
     </row>
@@ -6823,6 +7338,12 @@
         <v>2.903444978000007</v>
       </c>
       <c r="U62" t="n">
+        <v>81.19897096666679</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6894,6 +7415,12 @@
         <v>2.940431538000007</v>
       </c>
       <c r="U63" t="n">
+        <v>81.81541363333345</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1</v>
+      </c>
+      <c r="W63" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6965,6 +7492,12 @@
         <v>2.977418098000007</v>
       </c>
       <c r="U64" t="n">
+        <v>82.43185630000012</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="W64" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7036,6 +7569,12 @@
         <v>3.014404658000007</v>
       </c>
       <c r="U65" t="n">
+        <v>83.04829896666679</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1</v>
+      </c>
+      <c r="W65" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7107,6 +7646,12 @@
         <v>3.051391218000008</v>
       </c>
       <c r="U66" t="n">
+        <v>83.66474163333346</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1</v>
+      </c>
+      <c r="W66" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7178,6 +7723,12 @@
         <v>3.088377778000007</v>
       </c>
       <c r="U67" t="n">
+        <v>84.28118430000013</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1</v>
+      </c>
+      <c r="W67" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7249,6 +7800,12 @@
         <v>3.125364338000008</v>
       </c>
       <c r="U68" t="n">
+        <v>84.89762696666681</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7320,6 +7877,12 @@
         <v>3.162350898000009</v>
       </c>
       <c r="U69" t="n">
+        <v>85.51406963333348</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="W69" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7391,6 +7954,12 @@
         <v>3.199337458000009</v>
       </c>
       <c r="U70" t="n">
+        <v>86.13051230000015</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1</v>
+      </c>
+      <c r="W70" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7462,6 +8031,12 @@
         <v>3.236324018000009</v>
       </c>
       <c r="U71" t="n">
+        <v>86.74695496666682</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
+      <c r="W71" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7533,6 +8108,12 @@
         <v>3.273310578000009</v>
       </c>
       <c r="U72" t="n">
+        <v>87.36339763333349</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1</v>
+      </c>
+      <c r="W72" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7604,6 +8185,12 @@
         <v>3.310297138000009</v>
       </c>
       <c r="U73" t="n">
+        <v>87.97984030000016</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1</v>
+      </c>
+      <c r="W73" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7675,6 +8262,12 @@
         <v>3.32879045000001</v>
       </c>
       <c r="U74" t="n">
+        <v>92.97984136666683</v>
+      </c>
+      <c r="V74" t="n">
+        <v>1</v>
+      </c>
+      <c r="W74" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7746,6 +8339,12 @@
         <v>3.32879051400001</v>
       </c>
       <c r="U75" t="n">
+        <v>92.9798424333335</v>
+      </c>
+      <c r="V75" t="n">
+        <v>1</v>
+      </c>
+      <c r="W75" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7817,6 +8416,12 @@
         <v>3.32879057800001</v>
       </c>
       <c r="U76" t="n">
+        <v>92.97984350000017</v>
+      </c>
+      <c r="V76" t="n">
+        <v>1</v>
+      </c>
+      <c r="W76" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7888,6 +8493,12 @@
         <v>3.32879064200001</v>
       </c>
       <c r="U77" t="n">
+        <v>92.97984456666684</v>
+      </c>
+      <c r="V77" t="n">
+        <v>1</v>
+      </c>
+      <c r="W77" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7959,6 +8570,12 @@
         <v>3.328790706000011</v>
       </c>
       <c r="U78" t="n">
+        <v>92.97984563333351</v>
+      </c>
+      <c r="V78" t="n">
+        <v>1</v>
+      </c>
+      <c r="W78" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -8030,6 +8647,12 @@
         <v>3.328790770000011</v>
       </c>
       <c r="U79" t="n">
+        <v>92.97984670000018</v>
+      </c>
+      <c r="V79" t="n">
+        <v>1</v>
+      </c>
+      <c r="W79" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -8101,6 +8724,12 @@
         <v>3.328790834000011</v>
       </c>
       <c r="U80" t="n">
+        <v>92.97984776666685</v>
+      </c>
+      <c r="V80" t="n">
+        <v>1</v>
+      </c>
+      <c r="W80" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -8172,6 +8801,12 @@
         <v>3.328790898000011</v>
       </c>
       <c r="U81" t="n">
+        <v>92.97984883333352</v>
+      </c>
+      <c r="V81" t="n">
+        <v>1</v>
+      </c>
+      <c r="W81" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -8243,6 +8878,12 @@
         <v>3.328790962000011</v>
       </c>
       <c r="U82" t="n">
+        <v>92.97984990000019</v>
+      </c>
+      <c r="V82" t="n">
+        <v>1</v>
+      </c>
+      <c r="W82" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -8314,6 +8955,12 @@
         <v>3.328791026000011</v>
       </c>
       <c r="U83" t="n">
+        <v>92.97985096666686</v>
+      </c>
+      <c r="V83" t="n">
+        <v>1</v>
+      </c>
+      <c r="W83" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -8385,6 +9032,12 @@
         <v>3.328791090000012</v>
       </c>
       <c r="U84" t="n">
+        <v>92.97985203333353</v>
+      </c>
+      <c r="V84" t="n">
+        <v>1</v>
+      </c>
+      <c r="W84" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -8456,6 +9109,12 @@
         <v>3.328791154000012</v>
       </c>
       <c r="U85" t="n">
+        <v>92.9798531000002</v>
+      </c>
+      <c r="V85" t="n">
+        <v>1</v>
+      </c>
+      <c r="W85" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -12041,7 +12700,7 @@
         <v>51.38067</v>
       </c>
       <c r="F2" t="n">
-        <v>10.65214728000001</v>
+        <v>11.02201305000001</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -12050,13 +12709,13 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>858.16123728</v>
+        <v>858.5311030500001</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>858.16123728</v>
+        <v>858.5311030500001</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -12367,7 +13026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14246,7 +14905,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -14254,14 +14913,14 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>109.876</v>
+        <v>25.59377233333336</v>
       </c>
       <c r="G40" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -14278,7 +14937,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2035-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14295,7 +14954,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -14303,14 +14962,14 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>109.876</v>
       </c>
       <c r="G41" t="n">
-        <v>109.876</v>
+        <v>190</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -14344,7 +15003,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -14352,18 +15011,19 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>all_deliveries_ordered_within_lead_time</t>
+          <t>ordered_A_t</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>109.876</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42">
-        <f>=</f>
-        <v/>
+        <v>109.876</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="I42" t="b">
         <v>1</v>
@@ -14373,7 +15033,11 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -14388,7 +15052,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SOURCE_NOT_AVAILABLE</t>
+          <t>LEAD_TIME_VIOLATED</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -14396,7 +15060,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>all_orders_from_available_sources</t>
+          <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -14432,27 +15096,26 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
+          <t>all_orders_from_available_sources</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>23.42490800000007</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>70</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <f>=</f>
+        <v/>
       </c>
       <c r="I44" t="b">
         <v>1</v>
@@ -14462,11 +15125,7 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>2036-12, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -14481,7 +15140,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -14489,14 +15148,14 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>153.052</v>
+        <v>23.42490800000007</v>
       </c>
       <c r="G45" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -14513,7 +15172,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14530,7 +15189,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -14538,14 +15197,14 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>153.0518</v>
+        <v>35.09157466666673</v>
       </c>
       <c r="G46" t="n">
-        <v>153.052</v>
+        <v>70</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -14562,7 +15221,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14579,7 +15238,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -14587,170 +15246,170 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="G47" t="n">
+        <v>190</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>153.0518</v>
+      </c>
+      <c r="G48" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47">
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49">
         <f>=</f>
         <v/>
       </c>
-      <c r="I47" t="b">
-        <v>1</v>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
+      <c r="K49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D50" t="n">
         <v>2036</v>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48">
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50">
         <f>=</f>
         <v/>
       </c>
-      <c r="I48" t="b">
-        <v>1</v>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>25.44727350000007</v>
-      </c>
-      <c r="G49" t="n">
-        <v>70</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I49" t="b">
-        <v>1</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>2037-06, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>190</v>
-      </c>
-      <c r="G50" t="n">
-        <v>190</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I50" t="b">
-        <v>1</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -14765,7 +15424,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -14773,14 +15432,14 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>190</v>
+        <v>25.44727350000007</v>
       </c>
       <c r="G51" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -14797,7 +15456,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14814,7 +15473,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -14822,14 +15481,14 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>reserved_B_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>13.189</v>
+        <v>41.2806068333334</v>
       </c>
       <c r="G52" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -14846,7 +15505,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2037-06, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14863,7 +15522,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -14871,14 +15530,14 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ordered_B_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>13.1882</v>
+        <v>190</v>
       </c>
       <c r="G53" t="n">
-        <v>13.189</v>
+        <v>190</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -14895,7 +15554,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -14912,7 +15571,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -14920,219 +15579,219 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>190</v>
+      </c>
+      <c r="G54" t="n">
+        <v>190</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>13.189</v>
+      </c>
+      <c r="G55" t="n">
+        <v>110</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I55" t="b">
+        <v>1</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>13.1882</v>
+      </c>
+      <c r="G56" t="n">
+        <v>13.189</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I56" t="b">
+        <v>1</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54">
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57">
         <f>=</f>
         <v/>
       </c>
-      <c r="I54" t="b">
-        <v>1</v>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
+      <c r="K57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D58" t="n">
         <v>2037</v>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55">
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58">
         <f>=</f>
         <v/>
       </c>
-      <c r="I55" t="b">
-        <v>1</v>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="I58" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>39.45238750000007</v>
-      </c>
-      <c r="G56" t="n">
-        <v>120</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I56" t="b">
-        <v>1</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>2038-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>161.772</v>
-      </c>
-      <c r="G57" t="n">
-        <v>190</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>161.7714</v>
-      </c>
-      <c r="G58" t="n">
-        <v>161.772</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I58" t="b">
-        <v>1</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -15147,7 +15806,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -15155,11 +15814,11 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>120</v>
+        <v>39.45238750000007</v>
       </c>
       <c r="G59" t="n">
         <v>120</v>
@@ -15179,7 +15838,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2038-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -15196,7 +15855,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -15204,14 +15863,14 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>100</v>
+        <v>60.2857208333334</v>
       </c>
       <c r="G60" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -15228,7 +15887,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2038-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -15245,7 +15904,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -15253,268 +15912,268 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>161.772</v>
+      </c>
+      <c r="G61" t="n">
+        <v>190</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>161.7714</v>
+      </c>
+      <c r="G62" t="n">
+        <v>161.772</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>120</v>
+      </c>
+      <c r="G63" t="n">
+        <v>120</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I63" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>100</v>
+      </c>
+      <c r="G64" t="n">
+        <v>100</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61">
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65">
         <f>=</f>
         <v/>
       </c>
-      <c r="I61" t="b">
-        <v>1</v>
-      </c>
-      <c r="J61" t="inlineStr">
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
+      <c r="K65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D66" t="n">
         <v>2038</v>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F62" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" t="n">
-        <v>1</v>
-      </c>
-      <c r="H62">
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66">
         <f>=</f>
         <v/>
       </c>
-      <c r="I62" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>48.08252830000012</v>
-      </c>
-      <c r="G63" t="n">
-        <v>120</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I63" t="b">
-        <v>1</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>2039-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>152.622</v>
-      </c>
-      <c r="G64" t="n">
-        <v>190</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I64" t="b">
-        <v>1</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>152.6216</v>
-      </c>
-      <c r="G65" t="n">
-        <v>152.622</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I65" t="b">
-        <v>1</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>reserved_D_t_per_year</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>120</v>
-      </c>
-      <c r="G66" t="n">
-        <v>120</v>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I66" t="b">
-        <v>1</v>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Lunar-ISRU</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -15529,7 +16188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -15537,11 +16196,11 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>120</v>
+        <v>48.08252830000012</v>
       </c>
       <c r="G67" t="n">
         <v>120</v>
@@ -15561,7 +16220,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2039-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -15578,7 +16237,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -15586,14 +16245,14 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>reserved_X_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>60</v>
+        <v>74.74919496666678</v>
       </c>
       <c r="G68" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -15610,7 +16269,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Source-X</t>
+          <t>2039-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -15627,7 +16286,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -15635,14 +16294,14 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ordered_X_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>60</v>
+        <v>152.622</v>
       </c>
       <c r="G69" t="n">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -15659,7 +16318,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Source-X</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -15676,7 +16335,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -15684,317 +16343,317 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>152.6216</v>
+      </c>
+      <c r="G70" t="n">
+        <v>152.622</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>120</v>
+      </c>
+      <c r="G71" t="n">
+        <v>120</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>120</v>
+      </c>
+      <c r="G72" t="n">
+        <v>120</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>reserved_X_t_per_year</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>60</v>
+      </c>
+      <c r="G73" t="n">
+        <v>60</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Source-X</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ordered_X_t</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>60</v>
+      </c>
+      <c r="G74" t="n">
+        <v>60</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I74" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Source-X</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="n">
-        <v>1</v>
-      </c>
-      <c r="H70">
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75">
         <f>=</f>
         <v/>
       </c>
-      <c r="I70" t="b">
-        <v>1</v>
-      </c>
-      <c r="J70" t="inlineStr">
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
+      <c r="K75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D76" t="n">
         <v>2039</v>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="n">
-        <v>1</v>
-      </c>
-      <c r="H71">
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76">
         <f>=</f>
         <v/>
       </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" t="inlineStr">
+      <c r="I76" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>55.47984030000016</v>
-      </c>
-      <c r="G72" t="n">
-        <v>120</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I72" t="b">
-        <v>1</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>2040-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>190</v>
-      </c>
-      <c r="G73" t="n">
-        <v>190</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I73" t="b">
-        <v>1</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>190</v>
-      </c>
-      <c r="G74" t="n">
-        <v>190</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I74" t="b">
-        <v>1</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>32.224</v>
-      </c>
-      <c r="G75" t="n">
-        <v>110</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I75" t="b">
-        <v>1</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>ordered_B_t</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>32.224</v>
-      </c>
-      <c r="G76" t="n">
-        <v>32.224</v>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I76" t="b">
-        <v>1</v>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -16009,7 +16668,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -16017,11 +16676,11 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>120</v>
+        <v>55.47984030000016</v>
       </c>
       <c r="G77" t="n">
         <v>120</v>
@@ -16041,7 +16700,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2040-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -16058,7 +16717,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -16066,11 +16725,11 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>120</v>
+        <v>87.97984030000016</v>
       </c>
       <c r="G78" t="n">
         <v>120</v>
@@ -16090,7 +16749,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2040-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -16115,14 +16774,14 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>reserved_X_t_per_year</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="G79" t="n">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -16139,7 +16798,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Source-X</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -16164,14 +16823,14 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ordered_X_t</t>
+          <t>ordered_A_t</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="G80" t="n">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -16188,7 +16847,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Source-X</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -16205,7 +16864,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -16213,366 +16872,366 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>32.224</v>
+      </c>
+      <c r="G81" t="n">
+        <v>110</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I81" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>32.224</v>
+      </c>
+      <c r="G82" t="n">
+        <v>32.224</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>120</v>
+      </c>
+      <c r="G83" t="n">
+        <v>120</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I83" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>120</v>
+      </c>
+      <c r="G84" t="n">
+        <v>120</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I84" t="b">
+        <v>1</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>reserved_X_t_per_year</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>60</v>
+      </c>
+      <c r="G85" t="n">
+        <v>60</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I85" t="b">
+        <v>1</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Source-X</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>ordered_X_t</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>60</v>
+      </c>
+      <c r="G86" t="n">
+        <v>60</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I86" t="b">
+        <v>1</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Source-X</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F81" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" t="n">
-        <v>1</v>
-      </c>
-      <c r="H81">
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87">
         <f>=</f>
         <v/>
       </c>
-      <c r="I81" t="b">
-        <v>1</v>
-      </c>
-      <c r="J81" t="inlineStr">
+      <c r="I87" t="b">
+        <v>1</v>
+      </c>
+      <c r="J87" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
+      <c r="K87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D82" t="n">
+      <c r="D88" t="n">
         <v>2040</v>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F82" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" t="n">
-        <v>1</v>
-      </c>
-      <c r="H82">
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88">
         <f>=</f>
         <v/>
       </c>
-      <c r="I82" t="b">
-        <v>1</v>
-      </c>
-      <c r="J82" t="inlineStr">
+      <c r="I88" t="b">
+        <v>1</v>
+      </c>
+      <c r="J88" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>2041</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>55.4798531000002</v>
-      </c>
-      <c r="G83" t="n">
-        <v>120</v>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I83" t="b">
-        <v>1</v>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>2041-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>2041</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F84" t="n">
-        <v>190</v>
-      </c>
-      <c r="G84" t="n">
-        <v>190</v>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I84" t="b">
-        <v>1</v>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>2041</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F85" t="n">
-        <v>190</v>
-      </c>
-      <c r="G85" t="n">
-        <v>190</v>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I85" t="b">
-        <v>1</v>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>2041</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
-        <v>85.46599999999999</v>
-      </c>
-      <c r="G86" t="n">
-        <v>110</v>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I86" t="b">
-        <v>1</v>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>2041</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>ordered_B_t</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>85.46559999999999</v>
-      </c>
-      <c r="G87" t="n">
-        <v>85.46599999999999</v>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I87" t="b">
-        <v>1</v>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>2041</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>reserved_D_t_per_year</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
-        <v>120</v>
-      </c>
-      <c r="G88" t="n">
-        <v>120</v>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I88" t="b">
-        <v>1</v>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>Lunar-ISRU</t>
-        </is>
-      </c>
+      <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -16587,7 +17246,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -16595,11 +17254,11 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>120</v>
+        <v>55.4798531000002</v>
       </c>
       <c r="G89" t="n">
         <v>120</v>
@@ -16619,7 +17278,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2041-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -16636,7 +17295,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -16644,14 +17303,14 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>reserved_X_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>60</v>
+        <v>92.9798531000002</v>
       </c>
       <c r="G90" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -16668,7 +17327,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Source-X</t>
+          <t>2041-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -16685,7 +17344,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -16693,14 +17352,14 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ordered_X_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="G91" t="n">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -16717,7 +17376,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Source-X</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -16734,7 +17393,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -16742,72 +17401,415 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>190</v>
+      </c>
+      <c r="G92" t="n">
+        <v>190</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I92" t="b">
+        <v>1</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>2041</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>85.46599999999999</v>
+      </c>
+      <c r="G93" t="n">
+        <v>110</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I93" t="b">
+        <v>1</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>2041</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>85.46559999999999</v>
+      </c>
+      <c r="G94" t="n">
+        <v>85.46599999999999</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I94" t="b">
+        <v>1</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>2041</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>120</v>
+      </c>
+      <c r="G95" t="n">
+        <v>120</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I95" t="b">
+        <v>1</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>2041</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>120</v>
+      </c>
+      <c r="G96" t="n">
+        <v>120</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I96" t="b">
+        <v>1</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>2041</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>reserved_X_t_per_year</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>60</v>
+      </c>
+      <c r="G97" t="n">
+        <v>60</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I97" t="b">
+        <v>1</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Source-X</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>2041</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>ordered_X_t</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>60</v>
+      </c>
+      <c r="G98" t="n">
+        <v>60</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I98" t="b">
+        <v>1</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Source-X</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>2041</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F92" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" t="n">
-        <v>1</v>
-      </c>
-      <c r="H92">
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99">
         <f>=</f>
         <v/>
       </c>
-      <c r="I92" t="b">
-        <v>1</v>
-      </c>
-      <c r="J92" t="inlineStr">
+      <c r="I99" t="b">
+        <v>1</v>
+      </c>
+      <c r="J99" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>TEAM_2041_SOURCE_X</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_ext2041</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
+      <c r="K99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D100" t="n">
         <v>2041</v>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F93" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" t="n">
-        <v>1</v>
-      </c>
-      <c r="H93">
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100">
         <f>=</f>
         <v/>
       </c>
-      <c r="I93" t="b">
-        <v>1</v>
-      </c>
-      <c r="J93" t="inlineStr">
+      <c r="I100" t="b">
+        <v>1</v>
+      </c>
+      <c r="J100" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -29026,7 +30028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29068,7 +30070,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13273.29757753</v>
+        <v>13273.6674433</v>
       </c>
     </row>
     <row r="3">
@@ -29088,7 +30090,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10271.04259941365</v>
+        <v>10271.41246518365</v>
       </c>
     </row>
     <row r="4">
@@ -29228,7 +30230,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.213748683440217</v>
+        <v>7.213949697445653</v>
       </c>
     </row>
     <row r="11">
@@ -29248,7 +30250,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5.582088369246548</v>
+        <v>5.582289383251982</v>
       </c>
     </row>
     <row r="12">
@@ -29408,7 +30410,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>172.3357575300004</v>
+        <v>172.7056233000004</v>
       </c>
     </row>
     <row r="20">
@@ -29524,11 +30526,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>prep_holding_mln</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>0.36986577</v>
       </c>
     </row>
     <row r="26">
@@ -29544,11 +30546,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>prep_holding_months</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -29564,7 +30566,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -29584,11 +30586,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
-        <v>1</v>
+          <t>guideline_violations</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -29604,11 +30606,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>checks_total</t>
+          <t>warnings</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -29624,11 +30626,51 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TEAM_2041_SOURCE_X</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_ext2041</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>92</v>
+      <c r="D32" t="n">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
